--- a/data/trans_camb/IP1012-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,39</t>
+          <t>-1,22; 3,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,0</t>
+          <t>-3,05; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,13</t>
+          <t>-1,38; 3,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,95</t>
+          <t>-1,54; 0,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,89</t>
+          <t>-1,24; 1,49</t>
         </is>
       </c>
     </row>
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,3</t>
+          <t>-2,35; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,34</t>
+          <t>-2,27; 1,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,66</t>
+          <t>-1,19; 0,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,7</t>
+          <t>-1,13; 0,7</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,45</t>
+          <t>-2,77; 1,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 0,0</t>
+          <t>-4,37; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,73</t>
+          <t>-2,06; 0,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,0</t>
+          <t>-3,09; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,56</t>
+          <t>-1,24; 1,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,29</t>
+          <t>-1,74; 0,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,1</t>
+          <t>-0,5; 1,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,14</t>
+          <t>-0,87; 0,25</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,23</t>
+          <t>-1,88; 1,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,0</t>
+          <t>-3,11; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,99</t>
+          <t>0,47; 4,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,55</t>
+          <t>-0,19; 2,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,0</t>
+          <t>-1,4; 0,0</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 0,0</t>
+          <t>-5,46; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 0,0</t>
+          <t>-4,94; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,02; -0,89</t>
+          <t>-7,76; -0,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -0,89</t>
+          <t>-7,77; -0,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -0,5</t>
+          <t>-4,7; -0,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -0,5</t>
+          <t>-4,9; -0,49</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,57</t>
+          <t>-0,44; 0,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; -0,1</t>
+          <t>-0,93; -0,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,68</t>
+          <t>-0,93; 0,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,17</t>
+          <t>-1,24; 0,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,44</t>
+          <t>-0,53; 0,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; -0,03</t>
+          <t>-0,85; -0,05</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-75,72; 168,04</t>
+          <t>-74,58; 186,3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-90,14; 63,54</t>
+          <t>-92,06; 91,2</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-69,43; 140,89</t>
+          <t>-62,61; 144,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-93,21; 4,49</t>
+          <t>-93,65; -3,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1012-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,41</t>
+          <t>-1,22; 3,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,0</t>
+          <t>-3,52; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-4,05; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,47</t>
+          <t>-1,38; 3,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,95</t>
+          <t>-1,31; 0,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,49</t>
+          <t>-0,95; 1,57</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,32</t>
+          <t>-2,33; 1,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,35</t>
+          <t>-2,27; 1,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,66</t>
+          <t>-1,15; 0,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,99</t>
+          <t>-3,45; 1,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,0</t>
+          <t>-4,34; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,94</t>
+          <t>-2,07; 0,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,0</t>
+          <t>-2,9; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,47</t>
+          <t>-1,34; 1,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,49</t>
+          <t>-1,73; 0,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,07</t>
+          <t>-0,52; 1,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,25</t>
+          <t>-0,88; 0,24</t>
         </is>
       </c>
     </row>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,25</t>
+          <t>-1,87; 1,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,0</t>
+          <t>-3,09; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,94</t>
+          <t>0,47; 4,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,47</t>
+          <t>-0,08; 2,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,0</t>
+          <t>-1,39; 0,0</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,0</t>
+          <t>-4,5; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 0,0</t>
+          <t>-5,3; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -0,89</t>
+          <t>-8,32; -0,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,77; -0,88</t>
+          <t>-7,99; -0,89</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,7; -0,5</t>
+          <t>-4,77; -0,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -0,49</t>
+          <t>-4,78; -0,44</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,56</t>
+          <t>-0,43; 0,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; -0,1</t>
+          <t>-0,84; -0,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,74</t>
+          <t>-0,93; 0,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,2</t>
+          <t>-1,24; 0,14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,46</t>
+          <t>-0,56; 0,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; -0,05</t>
+          <t>-0,84; -0,02</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-74,58; 186,3</t>
+          <t>-71,69; 169,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-92,06; 91,2</t>
+          <t>-91,66; 69,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-62,61; 144,85</t>
+          <t>-68,97; 135,96</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-93,65; -3,93</t>
+          <t>-93,28; 16,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1012-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1012-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,67</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,61</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,3</t>
+          <t>-2,79; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,0</t>
+          <t>-1,38; 3,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,0</t>
+          <t>-1,22; 3,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,33</t>
+          <t>-3,06; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,94</t>
+          <t>-1,45; 0,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,57</t>
+          <t>-0,99; 1,89</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>39,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,38; 1,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,36; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,67</t>
+          <t>-1,13; 0,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,7</t>
+          <t>-1,17; 0,7</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-13,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-10,11%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-13,37%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,11%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,87</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,45; 1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,24; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,72</t>
+          <t>-2,07; 0,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,0</t>
+          <t>-2,08; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-18,22%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-18,22%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,37</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>-1,26; 1,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,83; 0,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,62</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,07</t>
+          <t>-0,52; 1,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,24</t>
+          <t>-1,02; 0,14</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-56,12%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-56,12%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,69</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,62</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,27 +1255,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,24</t>
+          <t>0,47; 4,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,88</t>
+          <t>-2,18; 1,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,12; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,42</t>
+          <t>-0,13; 2,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-0,47%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-2,98</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-2,98</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-0,98</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-0,98</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,0</t>
+          <t>-8,02; -0,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,0</t>
+          <t>-8,27; -0,89</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -0,89</t>
+          <t>-4,44; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,99; -0,89</t>
+          <t>-5,07; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,77; -0,5</t>
+          <t>-4,85; -0,5</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -0,44</t>
+          <t>-4,57; -0,5</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,31</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,64</t>
+          <t>-0,89; 0,68</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,84; -0,1</t>
+          <t>-1,27; 0,17</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,68</t>
+          <t>-0,51; 0,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,14</t>
+          <t>-0,87; -0,1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,45</t>
+          <t>-0,54; 0,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,84; -0,02</t>
+          <t>-0,83; -0,03</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-11,2%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-53,62%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>9,34%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-11,2%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-53,62%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,72; 168,04</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,14; 63,54</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-71,69; 169,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-91,66; 69,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-68,97; 135,96</t>
+          <t>-69,43; 140,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-93,28; 16,81</t>
+          <t>-93,21; 4,49</t>
         </is>
       </c>
     </row>
